--- a/MCF Languages.xlsx
+++ b/MCF Languages.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\audio_transscript\gemnai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\asr_transcriibe_script\asr_transcribe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C09D149-10D5-49D2-B0BF-080260FE1E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90361E06-CEEF-4C44-8F3A-F823AF276CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hausa" sheetId="1" r:id="rId1"/>
@@ -1485,139 +1485,143 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="76.33203125" style="1" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="255.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1632,127 +1636,128 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="255.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>57</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J4" s="1" t="s">
